--- a/tend_funil_ecom.xlsx
+++ b/tend_funil_ecom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr-my.sharepoint.com/personal/thiago_junio_claro_com_br/Documents/Documentos/Extração_VDI/FÍSICOS_MOBILIDADE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AF1DD26-F6AB-4CA4-851E-1B87D009BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{5AF1DD26-F6AB-4CA4-851E-1B87D009BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC6CF656-50BB-46D7-AD68-2C9791D31355}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A2A653BC-E116-4BD7-A304-2103DD4B8026}"/>
   </bookViews>
@@ -456,6 +456,7 @@
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="19.5546875" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -568,7 +569,7 @@
         <v>46113</v>
       </c>
       <c r="D8">
-        <v>5234</v>
+        <v>6972</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -582,7 +583,7 @@
         <v>46113</v>
       </c>
       <c r="D9">
-        <v>4270.9605544918995</v>
+        <v>5623.2082535630025</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -596,7 +597,7 @@
         <v>46113</v>
       </c>
       <c r="D10">
-        <v>3208.7971124029518</v>
+        <v>4139.1233869690604</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -694,7 +695,7 @@
         <v>46113</v>
       </c>
       <c r="D17">
-        <v>41086</v>
+        <v>95027</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -708,7 +709,7 @@
         <v>46113</v>
       </c>
       <c r="D18">
-        <v>23586.713899023682</v>
+        <v>51878.650597708896</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -722,7 +723,7 @@
         <v>46113</v>
       </c>
       <c r="D19">
-        <v>18774.747493370476</v>
+        <v>39985.738440205205</v>
       </c>
     </row>
   </sheetData>

--- a/tend_funil_ecom.xlsx
+++ b/tend_funil_ecom.xlsx
@@ -729,4 +729,237 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B1FCE07318A1814584838CBAD5908D62" ma:contentTypeVersion="12" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="a1bab300ec39fe626d5df437ad79fe57">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3e882393-2744-4d86-b319-76a87c80bc5a" xmlns:ns3="b51d5aa8-d092-4cd7-80a5-49acaba1ca64" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485dd4fda7d9371f833ace765ec112d1" ns2:_="" ns3:_="">
+    <xsd:import namespace="3e882393-2744-4d86-b319-76a87c80bc5a"/>
+    <xsd:import namespace="b51d5aa8-d092-4cd7-80a5-49acaba1ca64"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3e882393-2744-4d86-b319-76a87c80bc5a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="14" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="16" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Marcações de imagem" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="1c8a3b58-1317-4067-bbdf-e53778bd947f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b51d5aa8-d092-4cd7-80a5-49acaba1ca64" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{3323ae28-f984-42f9-8623-043e3117a243}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="b51d5aa8-d092-4cd7-80a5-49acaba1ca64">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de Conteúdo"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="b51d5aa8-d092-4cd7-80a5-49acaba1ca64" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3e882393-2744-4d86-b319-76a87c80bc5a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED92CDE-EBF7-4EBC-9FFA-F8DEB16D077F}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AFC27EF-9028-423E-B798-594BDB924DDA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4DDCA2-1C7C-4D08-B877-5E0DB09E1904}"/>
 </file>
--- a/tend_funil_ecom.xlsx
+++ b/tend_funil_ecom.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr-my.sharepoint.com/personal/thiago_junio_claro_com_br/Documents/Documentos/Extração_VDI/FÍSICOS_MOBILIDADE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://corpclarobr.sharepoint.com/sites/USER-CanaisEstratgicos/Documentos Compartilhados/Canais Estratégicos/Relatórios/Arquivos - Dashboard Canais Estratégicos/Arquivos_Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{5AF1DD26-F6AB-4CA4-851E-1B87D009BC5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC6CF656-50BB-46D7-AD68-2C9791D31355}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB3114AE-B998-4535-9458-D7A94FA22505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A2A653BC-E116-4BD7-A304-2103DD4B8026}"/>
   </bookViews>
@@ -499,7 +499,7 @@
         <v>46113</v>
       </c>
       <c r="D3">
-        <v>168246</v>
+        <v>172844</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -513,7 +513,7 @@
         <v>46113</v>
       </c>
       <c r="D4">
-        <v>21251.912688610977</v>
+        <v>21461.145738915329</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -527,7 +527,7 @@
         <v>46113</v>
       </c>
       <c r="D5">
-        <v>14167.332881475086</v>
+        <v>14613.849719197708</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -541,7 +541,7 @@
         <v>46113</v>
       </c>
       <c r="D6">
-        <v>8710.2954058811483</v>
+        <v>9104.4659540626581</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -555,7 +555,7 @@
         <v>46113</v>
       </c>
       <c r="D7">
-        <v>7625.284456077763</v>
+        <v>7906.3488355631816</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -569,7 +569,7 @@
         <v>46113</v>
       </c>
       <c r="D8">
-        <v>6972</v>
+        <v>7237</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -583,7 +583,7 @@
         <v>46113</v>
       </c>
       <c r="D9">
-        <v>5623.2082535630025</v>
+        <v>4436.176164833626</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -597,7 +597,7 @@
         <v>46113</v>
       </c>
       <c r="D10">
-        <v>4139.1233869690604</v>
+        <v>3359.3729585096894</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -625,7 +625,7 @@
         <v>46113</v>
       </c>
       <c r="D12">
-        <v>1127353</v>
+        <v>1112265</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -639,7 +639,7 @@
         <v>46113</v>
       </c>
       <c r="D13">
-        <v>647730.33601280418</v>
+        <v>645353.92091868713</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -653,7 +653,7 @@
         <v>46113</v>
       </c>
       <c r="D14">
-        <v>284623.64475477347</v>
+        <v>281453.13978168112</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -667,7 +667,7 @@
         <v>46113</v>
       </c>
       <c r="D15">
-        <v>82405.439870284841</v>
+        <v>82159.084645581024</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -681,7 +681,7 @@
         <v>46113</v>
       </c>
       <c r="D16">
-        <v>63036.912396527521</v>
+        <v>63031.583450065496</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -695,7 +695,7 @@
         <v>46113</v>
       </c>
       <c r="D17">
-        <v>95027</v>
+        <v>95852</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -709,7 +709,7 @@
         <v>46113</v>
       </c>
       <c r="D18">
-        <v>51878.650597708896</v>
+        <v>49312.234859739678</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -723,7 +723,7 @@
         <v>46113</v>
       </c>
       <c r="D19">
-        <v>39985.738440205205</v>
+        <v>38918.320369100336</v>
       </c>
     </row>
   </sheetData>
@@ -944,22 +944,22 @@
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <TaxCatchAll xmlns="b51d5aa8-d092-4cd7-80a5-49acaba1ca64" xsi:nil="true"/>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="3e882393-2744-4d86-b319-76a87c80bc5a">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="b51d5aa8-d092-4cd7-80a5-49acaba1ca64" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EED92CDE-EBF7-4EBC-9FFA-F8DEB16D077F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA9CBF9F-7CDF-4C4F-9C61-D9DEF2142C04}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AFC27EF-9028-423E-B798-594BDB924DDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6FB14913-2E26-49B5-ABC2-BBC187BBE5B8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4DDCA2-1C7C-4D08-B877-5E0DB09E1904}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{56549EC9-AC24-4953-8E50-6266F2B56738}"/>
 </file>